--- a/VerveStacks_GBR_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BCD7F0-6ACA-4EF0-85A2-83154FE9DF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6363FB-DD0A-4FE1-B6A5-72AD0507F5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="428">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1263,12 +1263,6 @@
   </si>
   <si>
     <t>grid node -- way/148382435</t>
-  </si>
-  <si>
-    <t>e_w227767019-275_GBR</t>
-  </si>
-  <si>
-    <t>grid node -- way/227767019-275</t>
   </si>
   <si>
     <t>e_w23281217_GBR</t>
@@ -6204,8 +6198,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3390966-B599-4974-A44F-BB2F660203B6}">
-  <dimension ref="B3:I22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A48C94-2786-42E2-A52B-CBC7F25F0920}">
+  <dimension ref="B3:I21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -6678,32 +6672,6 @@
         <v>395</v>
       </c>
       <c r="I21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>428</v>
-      </c>
-      <c r="D22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E22" t="s">
-        <v>429</v>
-      </c>
-      <c r="F22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" t="s">
-        <v>395</v>
-      </c>
-      <c r="I22" t="s">
         <v>241</v>
       </c>
     </row>
